--- a/Luban/DataTables/Datas/__enums__.xlsx
+++ b/Luban/DataTables/Datas/__enums__.xlsx
@@ -1,118 +1,381 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22020" windowHeight="18375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="21">
+    <font>
       <name val="等线"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <name val="Noto Sans SC"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="34">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -135,39 +398,444 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -423,118 +1091,866 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="21" outlineLevelRow="5"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col width="9" customWidth="1" style="1" min="1" max="1"/>
+    <col width="19" customWidth="1" style="1" min="2" max="2"/>
+    <col width="34" customWidth="1" style="1" min="3" max="3"/>
+    <col width="19.5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="14.125" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13" customWidth="1" style="1" min="6" max="6"/>
+    <col width="11.125" customWidth="1" style="1" min="7" max="7"/>
+    <col width="16.75" customWidth="1" style="1" min="8" max="8"/>
+    <col width="8.375" customWidth="1" style="1" min="9" max="9"/>
+    <col width="12.125" customWidth="1" style="1" min="10" max="10"/>
+    <col width="15.125" customWidth="1" style="1" min="11" max="11"/>
+    <col width="9" customWidth="1" style="1" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
+      <c r="L1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="9">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Sword</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>BowAndArrow</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>弓箭</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="6">
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Spear</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>长矛</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="7">
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>护甲</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>消耗品</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>货币</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>BuffType</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>增益</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>减益</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>DamageOverTime</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>持续伤害</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>BuffEffectType</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>ModifyStat</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>修改属性</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>DamageOverTime</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>持续伤害</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>HealOverTime</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>持续治疗</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>DamageAmplify</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>伤害放大</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>Invincible</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>无敌</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>Stun</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>眩晕</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>最大生命</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>耐力</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>StaminaRegen</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>耐力回复</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>AttackPower</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>攻击力</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>防御</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>CritMultiplier</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>暴击倍率</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="29">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>移速</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>SkillCooldownMult</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>技能冷却</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>ModOp</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
+      <c r="D31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>加法</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>Mul</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>乘法</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>EnemyTier</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>首领</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RarityTier</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>传说</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RelicTrigger</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>命中时</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>击杀时</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>OnPerfectBlock</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>完美格挡时</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>被动</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>